--- a/ebs_playwright_automation/test_data/ShippingData_EBS.xlsx
+++ b/ebs_playwright_automation/test_data/ShippingData_EBS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\struts_playwright_automation\ebs_playwright_automation\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFFF98A-4CCD-4C86-8047-45C2F5F38EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0160C2D5-82EC-413F-8966-B34F3D1054C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="578" xr2:uid="{82038ABE-7B8C-4146-9485-918A215A8E15}"/>
   </bookViews>
@@ -8469,7 +8469,7 @@
         <v>288</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>

--- a/ebs_playwright_automation/test_data/ShippingData_EBS.xlsx
+++ b/ebs_playwright_automation/test_data/ShippingData_EBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\struts_playwright_automation\ebs_playwright_automation\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0160C2D5-82EC-413F-8966-B34F3D1054C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961542F9-8B5D-4F36-8622-C06CD3A6C6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="578" xr2:uid="{82038ABE-7B8C-4146-9485-918A215A8E15}"/>
   </bookViews>
@@ -8063,7 +8063,7 @@
         <v>288</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
@@ -10891,7 +10891,7 @@
         <v>288</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
